--- a/Grupikaaslastele/andmed/palga kontroll.xlsx
+++ b/Grupikaaslastele/andmed/palga kontroll.xlsx
@@ -420,27 +420,27 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Tekst 1</t>
+          <t>Kande kuupäev</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>DATACORP</t>
+          <t>PROSYSTEM</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>TESTLAB</t>
+          <t>ELEKTRILABOR</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Tekst 2</t>
+          <t>PROJEKTBÜROO</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Tekst 3</t>
+          <t>KOKKU</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
@@ -450,793 +450,793 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Tekst 4</t>
+          <t>kokku_palgakulu</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Tekst 5</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>76359.36852746828</v>
+        <v>63913.43353678667</v>
       </c>
       <c r="C2" t="n">
-        <v>40994.4007819979</v>
+        <v>36519.28434363488</v>
       </c>
       <c r="D2" t="n">
-        <v>6097.972384031247</v>
+        <v>5222.892641427444</v>
       </c>
       <c r="E2" t="n">
-        <v>94259.14417642605</v>
+        <v>93691.31524849776</v>
       </c>
       <c r="F2" t="n">
-        <v>143345.40202239</v>
+        <v>164418.7234799924</v>
       </c>
       <c r="G2" t="n">
-        <v>93366.7652397098</v>
+        <v>96415.60608070115</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Tekst 6</t>
+          <t>30.06.2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>67656.27526560648</v>
+        <v>56628.87129533276</v>
       </c>
       <c r="C3" t="n">
-        <v>36319.10148229647</v>
+        <v>32354.35983539885</v>
       </c>
       <c r="D3" t="n">
-        <v>6060.413316721045</v>
+        <v>5190.723427807022</v>
       </c>
       <c r="E3" t="n">
-        <v>83909.7153227089</v>
+        <v>83404.23265457347</v>
       </c>
       <c r="F3" t="n">
-        <v>143344.6945177035</v>
+        <v>164417.9119644797</v>
       </c>
       <c r="G3" t="n">
-        <v>78357.34581546859</v>
+        <v>80916.06224417355</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Tekst 7</t>
+          <t>31.05.2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>67848.89576830185</v>
+        <v>56790.0962757674</v>
       </c>
       <c r="C4" t="n">
-        <v>36505.81771515792</v>
+        <v>32520.69336069417</v>
       </c>
       <c r="D4" t="n">
-        <v>6120.576246921252</v>
+        <v>5242.252773241946</v>
       </c>
       <c r="E4" t="n">
-        <v>84223.96054509417</v>
+        <v>83716.58482425503</v>
       </c>
       <c r="F4" t="n">
-        <v>143343.987013017</v>
+        <v>164417.100448967</v>
       </c>
       <c r="G4" t="n">
-        <v>78025.16531172743</v>
+        <v>80573.03456709627</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Tekst 8</t>
+          <t>30.04.2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>72059.69202178462</v>
+        <v>60314.56814704945</v>
       </c>
       <c r="C5" t="n">
-        <v>38745.83141672981</v>
+        <v>34516.17800593541</v>
       </c>
       <c r="D5" t="n">
-        <v>6120.576246921252</v>
+        <v>5242.252773241946</v>
       </c>
       <c r="E5" t="n">
-        <v>89207.27126425273</v>
+        <v>88669.87545350171</v>
       </c>
       <c r="F5" t="n">
-        <v>143343.2795083305</v>
+        <v>164416.2889334543</v>
       </c>
       <c r="G5" t="n">
-        <v>83722.35175855475</v>
+        <v>86456.25953280379</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Tekst 9</t>
+          <t>31.03.2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>70139.67512874675</v>
+        <v>58707.4978628244</v>
       </c>
       <c r="C6" t="n">
-        <v>38720.10260726188</v>
+        <v>34493.25785852847</v>
       </c>
       <c r="D6" t="n">
-        <v>6518.673036479155</v>
+        <v>5583.221321771733</v>
       </c>
       <c r="E6" t="n">
-        <v>87766.49488720788</v>
+        <v>87237.77849438187</v>
       </c>
       <c r="F6" t="n">
-        <v>143342.5720036439</v>
+        <v>164415.4774179416</v>
       </c>
       <c r="G6" t="n">
-        <v>84434.48537915516</v>
+        <v>87191.64748872528</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Tekst 10</t>
+          <t>28.02.2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>64118.41738322223</v>
+        <v>53667.65449916421</v>
       </c>
       <c r="C7" t="n">
-        <v>35442.33140857315</v>
+        <v>31573.30156852567</v>
       </c>
       <c r="D7" t="n">
-        <v>6059.386979162797</v>
+        <v>5189.844373173283</v>
       </c>
       <c r="E7" t="n">
-        <v>80319.87034756818</v>
+        <v>79836.01335661743</v>
       </c>
       <c r="F7" t="n">
-        <v>143341.8644989574</v>
+        <v>164414.6659024289</v>
       </c>
       <c r="G7" t="n">
-        <v>75807.94701495707</v>
+        <v>78283.4142150632</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Tekst 11</t>
+          <t>31.01.2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>66812.99367390932</v>
+        <v>55923.03751222147</v>
       </c>
       <c r="C8" t="n">
-        <v>35580.14930340208</v>
+        <v>31696.07469834073</v>
       </c>
       <c r="D8" t="n">
-        <v>5957.706251070572</v>
+        <v>5102.755174816371</v>
       </c>
       <c r="E8" t="n">
-        <v>82677.3012659174</v>
+        <v>82179.24281490962</v>
       </c>
       <c r="F8" t="n">
-        <v>143341.1569942709</v>
+        <v>164413.8543869162</v>
       </c>
       <c r="G8" t="n">
-        <v>78332.50165326733</v>
+        <v>80890.40680939381</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Tekst 12</t>
+          <t>31.12.2025</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>78561.44565052356</v>
+        <v>65756.59060528238</v>
       </c>
       <c r="C9" t="n">
-        <v>39765.82231163357</v>
+        <v>35424.82252343905</v>
       </c>
       <c r="D9" t="n">
-        <v>6337.072380190433</v>
+        <v>5427.680976280411</v>
       </c>
       <c r="E9" t="n">
-        <v>95582.11443089618</v>
+        <v>95006.3157639273</v>
       </c>
       <c r="F9" t="n">
-        <v>143278.1890771703</v>
+        <v>164341.6295062866</v>
       </c>
       <c r="G9" t="n">
-        <v>76555.47844850524</v>
+        <v>79055.35588022511</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Tekst 13</t>
+          <t>30.11.2025</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>69964.91544544931</v>
+        <v>58561.22253841122</v>
       </c>
       <c r="C10" t="n">
-        <v>37092.1774065688</v>
+        <v>33043.04363023838</v>
       </c>
       <c r="D10" t="n">
-        <v>6454.172608264921</v>
+        <v>5527.976924015648</v>
       </c>
       <c r="E10" t="n">
-        <v>86608.24443772054</v>
+        <v>86086.50549113331</v>
       </c>
       <c r="F10" t="n">
-        <v>143277.4815724838</v>
+        <v>164340.8179907739</v>
       </c>
       <c r="G10" t="n">
-        <v>79821.00767022942</v>
+        <v>82427.51917921523</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Tekst 14</t>
+          <t>31.10.2025</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>79513.97747496894</v>
+        <v>66553.86775185104</v>
       </c>
       <c r="C11" t="n">
-        <v>32153.45762896072</v>
+        <v>28643.45470073745</v>
       </c>
       <c r="D11" t="n">
-        <v>5967.932971740265</v>
+        <v>5111.514326345419</v>
       </c>
       <c r="E11" t="n">
-        <v>91660.03648958258</v>
+        <v>91107.86491293077</v>
       </c>
       <c r="F11" t="n">
-        <v>143276.7740677973</v>
+        <v>164340.0064752612</v>
       </c>
       <c r="G11" t="n">
-        <v>86022.07532724224</v>
+        <v>88831.07932144924</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Tekst 15</t>
+          <t>30.09.2025</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>74600.81954515264</v>
+        <v>62441.51325156348</v>
       </c>
       <c r="C12" t="n">
-        <v>27052.89733432469</v>
+        <v>24099.69242690358</v>
       </c>
       <c r="D12" t="n">
-        <v>5612.991232845873</v>
+        <v>4807.507932177156</v>
       </c>
       <c r="E12" t="n">
-        <v>84153.34744054827</v>
+        <v>83646.39710192326</v>
       </c>
       <c r="F12" t="n">
-        <v>143276.0665631107</v>
+        <v>164339.1949597485</v>
       </c>
       <c r="G12" t="n">
-        <v>76844.93108975385</v>
+        <v>79354.26043974362</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Tekst 16</t>
+          <t>31.08.2025</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>72065.08332749752</v>
+        <v>60319.08071526475</v>
       </c>
       <c r="C13" t="n">
-        <v>28772.67228299338</v>
+        <v>25631.72970905535</v>
       </c>
       <c r="D13" t="n">
-        <v>7892.132618892877</v>
+        <v>6759.584790565344</v>
       </c>
       <c r="E13" t="n">
-        <v>84348.13993038399</v>
+        <v>83840.01613732504</v>
       </c>
       <c r="F13" t="n">
-        <v>143275.3590584242</v>
+        <v>164338.3834442358</v>
       </c>
       <c r="G13" t="n">
-        <v>77313.05516163333</v>
+        <v>79837.67084809767</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Tekst 17</t>
+          <t>31.07.2025</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>74999.25907726504</v>
+        <v>62775.01049028061</v>
       </c>
       <c r="C14" t="n">
-        <v>30251.29373398213</v>
+        <v>26948.93879554524</v>
       </c>
       <c r="D14" t="n">
-        <v>6472.096860621481</v>
+        <v>5543.328985297743</v>
       </c>
       <c r="E14" t="n">
-        <v>86917.3660567466</v>
+        <v>86393.76492268607</v>
       </c>
       <c r="F14" t="n">
-        <v>143274.6515537377</v>
+        <v>164337.5719287232</v>
       </c>
       <c r="G14" t="n">
-        <v>81636.14696104692</v>
+        <v>84301.93085445907</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Tekst 18</t>
+          <t>30.06.2025</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>71929.5886254299</v>
+        <v>60205.67051030646</v>
       </c>
       <c r="C15" t="n">
-        <v>28425.40135539357</v>
+        <v>25322.36829609711</v>
       </c>
       <c r="D15" t="n">
-        <v>6430.872302031819</v>
+        <v>5508.020290842538</v>
       </c>
       <c r="E15" t="n">
-        <v>83145.02671001971</v>
+        <v>82644.15062216821</v>
       </c>
       <c r="F15" t="n">
-        <v>143273.9440490512</v>
+        <v>164336.7604132105</v>
       </c>
       <c r="G15" t="n">
-        <v>76057.56719630389</v>
+        <v>78541.18560740755</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Tekst 19</t>
+          <t>31.05.2025</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>72859.99575190253</v>
+        <v>60984.42909863305</v>
       </c>
       <c r="C16" t="n">
-        <v>30471.42898269741</v>
+        <v>27145.04318025478</v>
       </c>
       <c r="D16" t="n">
-        <v>6496.900018279161</v>
+        <v>5564.572805613116</v>
       </c>
       <c r="E16" t="n">
-        <v>85208.05993693038</v>
+        <v>84694.75587770535</v>
       </c>
       <c r="F16" t="n">
-        <v>143273.2365443647</v>
+        <v>164335.9488976978</v>
       </c>
       <c r="G16" t="n">
-        <v>78868.01268894502</v>
+        <v>81443.40466612806</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Tekst 20</t>
+          <t>30.04.2025</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>73853.86092014682</v>
+        <v>61816.30260151907</v>
       </c>
       <c r="C17" t="n">
-        <v>32236.77644059185</v>
+        <v>28717.67809015377</v>
       </c>
       <c r="D17" t="n">
-        <v>6496.900018279161</v>
+        <v>5564.572805613116</v>
       </c>
       <c r="E17" t="n">
-        <v>87119.51683490738</v>
+        <v>86594.69791915949</v>
       </c>
       <c r="F17" t="n">
-        <v>143272.5290396781</v>
+        <v>164335.1373821851</v>
       </c>
       <c r="G17" t="n">
-        <v>80283.87815253688</v>
+        <v>82905.50444489262</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Tekst 21</t>
+          <t>31.03.2025</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>70355.14086555575</v>
+        <v>58887.84449630976</v>
       </c>
       <c r="C18" t="n">
-        <v>39835.47926143767</v>
+        <v>35486.87543573635</v>
       </c>
       <c r="D18" t="n">
-        <v>6496.900018279161</v>
+        <v>5564.572805613116</v>
       </c>
       <c r="E18" t="n">
-        <v>88603.3991087935</v>
+        <v>88069.64109978187</v>
       </c>
       <c r="F18" t="n">
-        <v>143271.8215349916</v>
+        <v>164334.3258666724</v>
       </c>
       <c r="G18" t="n">
-        <v>82628.91407493861</v>
+        <v>85327.11623747101</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Tekst 22</t>
+          <t>28.02.2025</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>66676.99035809521</v>
+        <v>55809.20159328061</v>
       </c>
       <c r="C19" t="n">
-        <v>36290.85048295278</v>
+        <v>32329.19283067762</v>
       </c>
       <c r="D19" t="n">
-        <v>6496.900018279161</v>
+        <v>5564.572805613116</v>
       </c>
       <c r="E19" t="n">
-        <v>83306.31362724247</v>
+        <v>82804.46592673635</v>
       </c>
       <c r="F19" t="n">
-        <v>143271.1140303051</v>
+        <v>164333.5143511597</v>
       </c>
       <c r="G19" t="n">
-        <v>75827.92193736028</v>
+        <v>78304.04140767264</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Tekst 23</t>
+          <t>31.01.2025</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>70157.32402575031</v>
+        <v>58722.2701380198</v>
       </c>
       <c r="C20" t="n">
-        <v>35451.93798471759</v>
+        <v>31581.85945153152</v>
       </c>
       <c r="D20" t="n">
-        <v>6132.061452930227</v>
+        <v>5252.089813190936</v>
       </c>
       <c r="E20" t="n">
-        <v>85606.08379272286</v>
+        <v>85090.3819877799</v>
       </c>
       <c r="F20" t="n">
-        <v>143270.4065256185</v>
+        <v>164332.702835647</v>
       </c>
       <c r="G20" t="n">
-        <v>82200.58911865544</v>
+        <v>84884.80456314549</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Tekst 24</t>
+          <t>31.12.2024</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>151045.82167374</v>
+        <v>126426.6228325499</v>
       </c>
       <c r="C21" t="n">
-        <v>29424.22563722232</v>
+        <v>26212.1568345711</v>
       </c>
       <c r="D21" t="n">
-        <v>5176.174637072606</v>
+        <v>4433.376001095932</v>
       </c>
       <c r="E21" t="n">
-        <v>151591.5012684097</v>
+        <v>150678.2950177019</v>
       </c>
       <c r="F21" t="n">
-        <v>143207.438608518</v>
+        <v>164260.4779550174</v>
       </c>
       <c r="G21" t="n">
-        <v>69352.83398259214</v>
+        <v>71617.51298418071</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Tekst 25</t>
+          <t>30.11.2024</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>72446.56906805992</v>
+        <v>60638.38748789601</v>
       </c>
       <c r="C22" t="n">
-        <v>34828.35126528752</v>
+        <v>31026.34600858881</v>
       </c>
       <c r="D22" t="n">
-        <v>5353.914309213629</v>
+        <v>4585.609426774615</v>
       </c>
       <c r="E22" t="n">
-        <v>86752.33751239353</v>
+        <v>86229.73053101957</v>
       </c>
       <c r="F22" t="n">
-        <v>143206.7311038315</v>
+        <v>164259.6664395047</v>
       </c>
       <c r="G22" t="n">
-        <v>81948.55126473379</v>
+        <v>84624.53655044583</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Tekst 26</t>
+          <t>31.10.2024</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>65932.30354115709</v>
+        <v>55185.89246569171</v>
       </c>
       <c r="C23" t="n">
-        <v>37740.55329610132</v>
+        <v>33620.6401560984</v>
       </c>
       <c r="D23" t="n">
-        <v>5370.751132490616</v>
+        <v>4600.03010874239</v>
       </c>
       <c r="E23" t="n">
-        <v>82844.94674398047</v>
+        <v>82345.87837554864</v>
       </c>
       <c r="F23" t="n">
-        <v>143206.0235991449</v>
+        <v>164258.854923992</v>
       </c>
       <c r="G23" t="n">
-        <v>80067.33652582392</v>
+        <v>82681.89176935835</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Tekst 27</t>
+          <t>30.09.2024</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>64536.39616009602</v>
+        <v>54017.50625004531</v>
       </c>
       <c r="C24" t="n">
-        <v>36152.77295093075</v>
+        <v>32206.18840672727</v>
       </c>
       <c r="D24" t="n">
-        <v>5387.148096814068</v>
+        <v>4614.074053009991</v>
       </c>
       <c r="E24" t="n">
-        <v>80700.2887083172</v>
+        <v>80214.14002936275</v>
       </c>
       <c r="F24" t="n">
-        <v>143205.3160944584</v>
+        <v>164258.0434084793</v>
       </c>
       <c r="G24" t="n">
-        <v>76299.44499177652</v>
+        <v>78790.96179048601</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Tekst 28</t>
+          <t>31.08.2024</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>68653.86179109602</v>
+        <v>57463.85960552462</v>
       </c>
       <c r="C25" t="n">
-        <v>34493.18437635619</v>
+        <v>30727.76730793782</v>
       </c>
       <c r="D25" t="n">
-        <v>5459.517112974877</v>
+        <v>4676.057869624746</v>
       </c>
       <c r="E25" t="n">
-        <v>83327.66074941623</v>
+        <v>82825.68445116392</v>
       </c>
       <c r="F25" t="n">
-        <v>143204.6085897719</v>
+        <v>164257.2318929666</v>
       </c>
       <c r="G25" t="n">
-        <v>79750.0960029134</v>
+        <v>82354.29193004458</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Tekst 29</t>
+          <t>31.07.2024</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>68174.60353466474</v>
+        <v>57062.71641497614</v>
       </c>
       <c r="C26" t="n">
-        <v>34050.88623608434</v>
+        <v>30333.75224146216</v>
       </c>
       <c r="D26" t="n">
-        <v>5632.540519669661</v>
+        <v>4824.251829962672</v>
       </c>
       <c r="E26" t="n">
-        <v>82753.18499257026</v>
+        <v>82254.66940845853</v>
       </c>
       <c r="F26" t="n">
-        <v>143203.9010850854</v>
+        <v>164256.4203774539</v>
       </c>
       <c r="G26" t="n">
-        <v>79949.4247973381</v>
+        <v>82560.12969763191</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Tekst 30</t>
+          <t>30.06.2024</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>65362.41031509949</v>
+        <v>54708.88704344814</v>
       </c>
       <c r="C27" t="n">
-        <v>35103.1463249868</v>
+        <v>31271.14331578085</v>
       </c>
       <c r="D27" t="n">
-        <v>5361.453002945053</v>
+        <v>4592.066292358154</v>
       </c>
       <c r="E27" t="n">
-        <v>80777.06189839396</v>
+        <v>80290.45072809614</v>
       </c>
       <c r="F27" t="n">
-        <v>143203.1935803989</v>
+        <v>164255.6088619413</v>
       </c>
       <c r="G27" t="n">
-        <v>74078.03020085164</v>
+        <v>76497.00791006857</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Tekst 31</t>
+          <t>31.05.2024</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>70112.41343193434</v>
+        <v>58684.67959335831</v>
       </c>
       <c r="C28" t="n">
-        <v>31348.45869361383</v>
+        <v>27926.33274126325</v>
       </c>
       <c r="D28" t="n">
-        <v>5227.77253598314</v>
+        <v>4477.569426313577</v>
       </c>
       <c r="E28" t="n">
-        <v>82583.32688235349</v>
+        <v>82085.83454483992</v>
       </c>
       <c r="F28" t="n">
-        <v>143202.4860757123</v>
+        <v>164254.7973464286</v>
       </c>
       <c r="G28" t="n">
-        <v>80496.40429935188</v>
+        <v>83124.97051722099</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Tekst 32</t>
+          <t>30.04.2024</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>68783.10902097746</v>
+        <v>57572.04062373027</v>
       </c>
       <c r="C29" t="n">
-        <v>27114.0851661636</v>
+        <v>24154.20074478774</v>
       </c>
       <c r="D29" t="n">
-        <v>4991.922608758408</v>
+        <v>4275.564764467451</v>
       </c>
       <c r="E29" t="n">
-        <v>78771.10870029854</v>
+        <v>78296.58164410869</v>
       </c>
       <c r="F29" t="n">
-        <v>143201.7785710258</v>
+        <v>164253.9858309159</v>
       </c>
       <c r="G29" t="n">
-        <v>75596.14484423556</v>
+        <v>78064.69575987312</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Tekst 33</t>
+          <t>31.03.2024</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>62449.46918924837</v>
+        <v>52270.73082720486</v>
       </c>
       <c r="C30" t="n">
-        <v>27094.87201387472</v>
+        <v>24137.08497877603</v>
       </c>
       <c r="D30" t="n">
-        <v>5220.930285594814</v>
+        <v>4471.709062088647</v>
       </c>
       <c r="E30" t="n">
-        <v>73405.10082980078</v>
+        <v>72962.89927924736</v>
       </c>
       <c r="F30" t="n">
-        <v>143201.0710663393</v>
+        <v>164253.1743154032</v>
       </c>
       <c r="G30" t="n">
-        <v>69003.63171267061</v>
+        <v>71256.90770442404</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Tekst 34</t>
+          <t>29.02.2024</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>63850.68310706459</v>
+        <v>53443.55865873612</v>
       </c>
       <c r="C31" t="n">
-        <v>29797.73228500039</v>
+        <v>26544.88996920043</v>
       </c>
       <c r="D31" t="n">
-        <v>4677.093562765575</v>
+        <v>4005.914755567843</v>
       </c>
       <c r="E31" t="n">
-        <v>75900.01633011148</v>
+        <v>75442.78509510473</v>
       </c>
       <c r="F31" t="n">
-        <v>143200.3635616528</v>
+        <v>164252.3627998905</v>
       </c>
       <c r="G31" t="n">
-        <v>73993.50212739511</v>
+        <v>76409.71961843481</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Tekst 35</t>
+          <t>31.01.2024</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>58023.74124339042</v>
+        <v>48566.35932211916</v>
       </c>
       <c r="C32" t="n">
-        <v>26675.03867264335</v>
+        <v>23763.08236200648</v>
       </c>
       <c r="D32" t="n">
-        <v>4552.931154825995</v>
+        <v>3899.570074757589</v>
       </c>
       <c r="E32" t="n">
-        <v>68915.72164653154</v>
+        <v>68500.56468025665</v>
       </c>
       <c r="F32" t="n">
-        <v>143199.6560569663</v>
+        <v>164251.5512843778</v>
       </c>
       <c r="G32" t="n">
-        <v>67575.64807056839</v>
+        <v>69782.29403463338</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Tekst 36</t>
+          <t>31.12.2023</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>57299.66176008134</v>
+        <v>47960.29870605765</v>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
@@ -1247,11 +1247,11 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Tekst 37</t>
+          <t>30.11.2023</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>60098.0461164291</v>
+        <v>50302.56994295869</v>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
@@ -1262,11 +1262,11 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Tekst 38</t>
+          <t>31.10.2023</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>56971.97887700287</v>
+        <v>47686.02537754989</v>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
@@ -1277,11 +1277,11 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Tekst 39</t>
+          <t>30.09.2023</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>48668.56277403665</v>
+        <v>40735.9962788374</v>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
@@ -1292,11 +1292,11 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Tekst 40</t>
+          <t>31.08.2023</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>49349.5881037045</v>
+        <v>41306.02020627385</v>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
@@ -1307,11 +1307,11 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Tekst 41</t>
+          <t>31.07.2023</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>48321.3745537799</v>
+        <v>40445.39681909786</v>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
@@ -1322,11 +1322,11 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Tekst 42</t>
+          <t>30.06.2023</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>49471.10440463915</v>
+        <v>41407.73037194434</v>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
@@ -1337,11 +1337,11 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Tekst 43</t>
+          <t>31.05.2023</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>44747.04058887581</v>
+        <v>37453.64923514555</v>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
@@ -1352,11 +1352,11 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Tekst 44</t>
+          <t>30.04.2023</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>47654.81928519998</v>
+        <v>39887.4844544657</v>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
@@ -1367,11 +1367,11 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Tekst 45</t>
+          <t>31.03.2023</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>44755.78874531561</v>
+        <v>37460.97151564586</v>
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
@@ -1382,11 +1382,11 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Tekst 46</t>
+          <t>28.02.2023</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>42391.78595916626</v>
+        <v>35482.28130556399</v>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
@@ -1397,11 +1397,11 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Tekst 47</t>
+          <t>31.01.2023</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>54807.71718599989</v>
+        <v>45874.52014365874</v>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
@@ -1412,11 +1412,11 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Tekst 48</t>
+          <t>31.12.2022</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>49321.67368591742</v>
+        <v>41282.65560386346</v>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
@@ -1427,11 +1427,11 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Tekst 49</t>
+          <t>30.11.2022</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>37697.50995515627</v>
+        <v>31553.13281767808</v>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
@@ -1442,11 +1442,11 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Tekst 50</t>
+          <t>31.10.2022</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>35922.47341055825</v>
+        <v>30067.41230418637</v>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
@@ -1457,11 +1457,11 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Tekst 51</t>
+          <t>30.09.2022</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>37870.50644413251</v>
+        <v>31697.93233361833</v>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
@@ -1472,11 +1472,11 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Tekst 52</t>
+          <t>31.08.2022</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>38507.7062226436</v>
+        <v>32231.2739062228</v>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
@@ -1487,11 +1487,11 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Tekst 53</t>
+          <t>31.07.2022</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>35589.22968385139</v>
+        <v>29788.48450280246</v>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
@@ -1502,11 +1502,11 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Tekst 54</t>
+          <t>30.06.2022</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>34970.45867675514</v>
+        <v>29270.56796683334</v>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
@@ -1517,11 +1517,11 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Tekst 55</t>
+          <t>31.05.2022</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>33570.5756315756</v>
+        <v>28098.85408688981</v>
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
@@ -1532,11 +1532,11 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Tekst 56</t>
+          <t>30.04.2022</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>31203.12274884581</v>
+        <v>26117.27611695946</v>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
@@ -1547,11 +1547,11 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Tekst 57</t>
+          <t>31.03.2022</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>28719.42619435343</v>
+        <v>24038.40121631133</v>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
@@ -1562,11 +1562,11 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Tekst 58</t>
+          <t>28.02.2022</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>26561.71714378451</v>
+        <v>22232.38059756235</v>
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
@@ -1577,11 +1577,11 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Tekst 59</t>
+          <t>31.01.2022</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>35797.49005925163</v>
+        <v>29962.80018820132</v>
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
@@ -1592,11 +1592,11 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Tekst 60</t>
+          <t>31.12.2021</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>41292.21390060769</v>
+        <v>34561.93024663257</v>
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
@@ -1607,11 +1607,11 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Tekst 61</t>
+          <t>30.11.2021</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>39307.23007835021</v>
+        <v>32900.48209636645</v>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
@@ -1622,11 +1622,11 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Tekst 62</t>
+          <t>31.10.2021</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>35436.45906819431</v>
+        <v>29660.61421290267</v>
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
@@ -1637,11 +1637,11 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Tekst 63</t>
+          <t>30.09.2021</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>35761.75994356</v>
+        <v>29932.89378092534</v>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
@@ -1652,11 +1652,11 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Tekst 64</t>
+          <t>31.08.2021</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>39124.17151408904</v>
+        <v>32747.26053880424</v>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
@@ -1667,11 +1667,11 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Tekst 65</t>
+          <t>31.07.2021</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>39828.06750855786</v>
+        <v>33336.42740499054</v>
       </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
@@ -1682,11 +1682,11 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Tekst 66</t>
+          <t>30.06.2021</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>34275.51428422474</v>
+        <v>28688.89366674038</v>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
@@ -1697,11 +1697,11 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Tekst 67</t>
+          <t>31.05.2021</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>36470.02153935293</v>
+        <v>30525.71469212875</v>
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
@@ -1712,11 +1712,11 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Tekst 68</t>
+          <t>30.04.2021</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>31718.19588992646</v>
+        <v>26548.39666711435</v>
       </c>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
@@ -1727,11 +1727,11 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Tekst 69</t>
+          <t>31.03.2021</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>29379.55597593591</v>
+        <v>24590.93539429694</v>
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
@@ -1742,11 +1742,11 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Tekst 70</t>
+          <t>28.02.2021</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>28594.62933475386</v>
+        <v>23933.94519545322</v>
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
@@ -1757,11 +1757,11 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Tekst 71</t>
+          <t>31.01.2021</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>30888.97746832003</v>
+        <v>25854.33387562129</v>
       </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
@@ -1772,11 +1772,11 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Tekst 72</t>
+          <t>31.12.2020</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>40626.94712018556</v>
+        <v>34005.09635742293</v>
       </c>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr"/>
@@ -1787,11 +1787,11 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Tekst 73</t>
+          <t>30.11.2020</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>42822.84458622086</v>
+        <v>35843.08100103033</v>
       </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr"/>
@@ -1802,11 +1802,11 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Tekst 74</t>
+          <t>31.10.2020</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>36999.52235704263</v>
+        <v>30968.91132892271</v>
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr"/>
@@ -1817,11 +1817,11 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Tekst 75</t>
+          <t>30.09.2020</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>36536.35324879232</v>
+        <v>30581.23489068972</v>
       </c>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr"/>
@@ -1832,11 +1832,11 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Tekst 76</t>
+          <t>31.08.2020</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>34186.24409481819</v>
+        <v>28614.17376756523</v>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
@@ -1847,11 +1847,11 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Tekst 77</t>
+          <t>31.07.2020</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>43145.22093254417</v>
+        <v>36112.9127136532</v>
       </c>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr"/>
@@ -1862,11 +1862,11 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Tekst 78</t>
+          <t>30.06.2020</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>34393.68221132826</v>
+        <v>28787.80121535892</v>
       </c>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr"/>
@@ -1877,11 +1877,11 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Tekst 79</t>
+          <t>31.05.2020</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>34926.82809420121</v>
+        <v>29234.04880236134</v>
       </c>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr"/>
@@ -1892,11 +1892,11 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Tekst 80</t>
+          <t>30.04.2020</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>33566.09135371062</v>
+        <v>28095.1007086101</v>
       </c>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr"/>
@@ -1907,11 +1907,11 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Tekst 81</t>
+          <t>31.03.2020</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>31319.05277546474</v>
+        <v>26214.31052405466</v>
       </c>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr"/>
@@ -1922,11 +1922,11 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Tekst 82</t>
+          <t>29.02.2020</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>30059.80990808825</v>
+        <v>25160.31365552649</v>
       </c>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr"/>
@@ -1937,11 +1937,11 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Tekst 83</t>
+          <t>31.01.2020</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>442723.1577630501</v>
+        <v>370563.0057522843</v>
       </c>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr"/>
@@ -1952,11 +1952,11 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Tekst 84</t>
+          <t>31.12.2019</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>35336.43169804929</v>
+        <v>29576.89046299602</v>
       </c>
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr"/>
@@ -1967,11 +1967,11 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Tekst 85</t>
+          <t>30.11.2019</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>39427.23749183691</v>
+        <v>33000.9293105553</v>
       </c>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr"/>
@@ -1982,11 +1982,11 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Tekst 86</t>
+          <t>31.10.2019</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>37454.48583018275</v>
+        <v>31349.71958157014</v>
       </c>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr"/>
@@ -1997,11 +1997,11 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Tekst 87</t>
+          <t>30.09.2019</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>35101.2656554592</v>
+        <v>29380.05450791889</v>
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr"/>
@@ -2012,11 +2012,11 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Tekst 88</t>
+          <t>31.08.2019</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>32925.83141582474</v>
+        <v>27559.19775687713</v>
       </c>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr"/>
@@ -2027,11 +2027,11 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Tekst 89</t>
+          <t>31.07.2019</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>39446.24269216446</v>
+        <v>33016.83682303756</v>
       </c>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr"/>
@@ -2042,11 +2042,11 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Tekst 90</t>
+          <t>30.06.2019</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>33348.98957601705</v>
+        <v>27913.38469514746</v>
       </c>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr"/>
@@ -2057,11 +2057,11 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Tekst 91</t>
+          <t>31.05.2019</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>35513.3021283947</v>
+        <v>29724.93250043689</v>
       </c>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr"/>
@@ -2072,11 +2072,11 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Tekst 92</t>
+          <t>30.04.2019</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>32361.23624962653</v>
+        <v>27086.6268552854</v>
       </c>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr"/>
@@ -2087,11 +2087,11 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Tekst 93</t>
+          <t>31.03.2019</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>25972.90348635713</v>
+        <v>21739.53861516696</v>
       </c>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr"/>
@@ -2102,11 +2102,11 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Tekst 94</t>
+          <t>28.02.2019</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>26975.75416412292</v>
+        <v>22578.93306507848</v>
       </c>
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr"/>
@@ -2117,11 +2117,11 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Tekst 95</t>
+          <t>31.01.2019</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>28205.96366347003</v>
+        <v>23608.6287604346</v>
       </c>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr"/>
@@ -2132,11 +2132,11 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Tekst 96</t>
+          <t>31.12.2018</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>25653.13802393251</v>
+        <v>21471.89223432132</v>
       </c>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr"/>
@@ -2147,11 +2147,11 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Tekst 97</t>
+          <t>30.11.2018</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>27524.0143521627</v>
+        <v>23037.83145259647</v>
       </c>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr"/>
@@ -2162,11 +2162,11 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Tekst 98</t>
+          <t>31.10.2018</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>29874.70841194531</v>
+        <v>25005.38214680093</v>
       </c>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr"/>
@@ -2177,11 +2177,11 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Tekst 99</t>
+          <t>30.09.2018</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>27090.41265637559</v>
+        <v>22674.90318721723</v>
       </c>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr"/>
@@ -2192,11 +2192,11 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Tekst 100</t>
+          <t>31.08.2018</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>24798.19222364895</v>
+        <v>20756.29541054295</v>
       </c>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr"/>
@@ -2207,11 +2207,11 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Tekst 101</t>
+          <t>31.07.2018</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>28926.72868053109</v>
+        <v>24211.91514037633</v>
       </c>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr"/>
@@ -2222,11 +2222,11 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Tekst 102</t>
+          <t>30.06.2018</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>25008.19036268306</v>
+        <v>20932.0656187156</v>
       </c>
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr"/>
@@ -2237,11 +2237,11 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Tekst 103</t>
+          <t>31.05.2018</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>24682.07570532298</v>
+        <v>20659.10490832081</v>
       </c>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr"/>
@@ -2252,11 +2252,11 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Tekst 104</t>
+          <t>30.04.2018</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>22894.48487808218</v>
+        <v>19162.8763546925</v>
       </c>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr"/>
@@ -2267,11 +2267,11 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Tekst 105</t>
+          <t>31.03.2018</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>22148.26374300879</v>
+        <v>18538.28298992283</v>
       </c>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr"/>
@@ -2282,11 +2282,11 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Tekst 106</t>
+          <t>28.02.2018</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>22269.06798469834</v>
+        <v>18639.39715601772</v>
       </c>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr"/>
@@ -2297,11 +2297,11 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Tekst 106</t>
+          <t>28.02.2018</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>22269.06798469834</v>
+        <v>18639.39715601772</v>
       </c>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr"/>
@@ -2312,11 +2312,11 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Tekst 107</t>
+          <t>31.01.2018</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>29547.08486713727</v>
+        <v>24731.15848492449</v>
       </c>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr"/>
@@ -2327,11 +2327,11 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Tekst 108</t>
+          <t>31.12.2017</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>434186.3557656066</v>
+        <v>363417.6306974337</v>
       </c>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr"/>
@@ -2342,11 +2342,11 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Tekst 109</t>
+          <t>30.11.2017</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>22604.28682812077</v>
+        <v>18919.97814670063</v>
       </c>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr"/>
@@ -2357,11 +2357,11 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Tekst 110</t>
+          <t>31.10.2017</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>20629.82283352007</v>
+        <v>17267.3351806408</v>
       </c>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr"/>
@@ -2372,11 +2372,11 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Tekst 111</t>
+          <t>30.09.2017</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>18790.63314169684</v>
+        <v>15727.91794348015</v>
       </c>
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr"/>
@@ -2387,11 +2387,11 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Tekst 112</t>
+          <t>31.08.2017</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>17312.46596403515</v>
+        <v>14490.67958638511</v>
       </c>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr"/>
@@ -2402,11 +2402,11 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Tekst 113</t>
+          <t>31.07.2017</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>21738.71100053536</v>
+        <v>18195.48390068641</v>
       </c>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr"/>
@@ -2417,11 +2417,11 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Tekst 114</t>
+          <t>30.06.2017</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>26057.56224446207</v>
+        <v>21810.39870756676</v>
       </c>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr"/>
@@ -2432,11 +2432,11 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Tekst 115</t>
+          <t>31.05.2017</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>24387.63073057829</v>
+        <v>20412.65198857442</v>
       </c>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr"/>
@@ -2447,11 +2447,11 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Tekst 116</t>
+          <t>30.04.2017</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>23553.80087767026</v>
+        <v>19714.729390306</v>
       </c>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr"/>
@@ -2462,11 +2462,11 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Tekst 117</t>
+          <t>31.03.2017</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>22991.47751953975</v>
+        <v>19244.06001116978</v>
       </c>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr"/>
@@ -2477,11 +2477,11 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Tekst 118</t>
+          <t>28.02.2017</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>21384.55477195156</v>
+        <v>17899.05215938558</v>
       </c>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr"/>
@@ -2492,11 +2492,11 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Tekst 119</t>
+          <t>31.01.2017</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>21771.68612510011</v>
+        <v>18223.08435722344</v>
       </c>
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr"/>
@@ -2507,11 +2507,11 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Tekst 120</t>
+          <t>31.12.2016</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>24662.17195404328</v>
+        <v>20642.44530113599</v>
       </c>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr"/>
@@ -2522,11 +2522,11 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Tekst 121</t>
+          <t>30.11.2016</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>19711.85979004514</v>
+        <v>16498.99239442124</v>
       </c>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr"/>
@@ -2537,11 +2537,11 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Tekst 122</t>
+          <t>31.10.2016</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>19403.24992246043</v>
+        <v>16240.6833402601</v>
       </c>
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr"/>
@@ -2552,11 +2552,11 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Tekst 123</t>
+          <t>30.09.2016</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>19012.93125650048</v>
+        <v>15913.98333479811</v>
       </c>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr"/>
@@ -2567,11 +2567,11 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Tekst 124</t>
+          <t>31.08.2016</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>21233.30999753399</v>
+        <v>17772.45901143352</v>
       </c>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr"/>
@@ -2582,11 +2582,11 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Tekst 125</t>
+          <t>31.07.2016</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>18492.61939383088</v>
+        <v>15478.47793062268</v>
       </c>
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr"/>
@@ -2597,11 +2597,11 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Tekst 126</t>
+          <t>30.06.2016</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>19860.4343422936</v>
+        <v>16623.35054396479</v>
       </c>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr"/>
@@ -2612,11 +2612,11 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Tekst 127</t>
+          <t>31.05.2016</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>19809.90356657881</v>
+        <v>16581.05585979584</v>
       </c>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr"/>
@@ -2627,11 +2627,11 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Tekst 128</t>
+          <t>30.04.2016</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>19288.82878328946</v>
+        <v>16144.91188464655</v>
       </c>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr"/>
@@ -2642,11 +2642,11 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Tekst 129</t>
+          <t>31.03.2016</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>18612.42336181898</v>
+        <v>15578.7548592185</v>
       </c>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr"/>
@@ -2657,11 +2657,11 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Tekst 130</t>
+          <t>29.02.2016</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>16711.11497775653</v>
+        <v>13987.34375431921</v>
       </c>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr"/>
@@ -2672,11 +2672,11 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Tekst 131</t>
+          <t>31.01.2016</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>17467.03368159653</v>
+        <v>14620.05406569</v>
       </c>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr"/>
@@ -2687,11 +2687,11 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Tekst 132</t>
+          <t>31.12.2015</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>65420.80765009348</v>
+        <v>54757.76610388093</v>
       </c>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr"/>
@@ -2702,11 +2702,11 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Tekst 133</t>
+          <t>30.11.2015</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>20494.90456036514</v>
+        <v>17154.40745152943</v>
       </c>
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr"/>
@@ -2717,11 +2717,11 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Tekst 134</t>
+          <t>31.10.2015</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>21185.9326270475</v>
+        <v>17732.80375395654</v>
       </c>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr"/>
@@ -2732,11 +2732,11 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Tekst 135</t>
+          <t>30.09.2015</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>20631.46735130042</v>
+        <v>17268.71165585113</v>
       </c>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr"/>
@@ -2747,11 +2747,11 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Tekst 136</t>
+          <t>31.08.2015</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>17934.33951498504</v>
+        <v>15011.19297764795</v>
       </c>
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr"/>
@@ -2762,11 +2762,11 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Tekst 137</t>
+          <t>31.07.2015</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>22637.45692128835</v>
+        <v>18947.74179359764</v>
       </c>
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr"/>
@@ -2777,11 +2777,11 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Tekst 138</t>
+          <t>30.06.2015</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>18839.12098552985</v>
+        <v>15768.50267648574</v>
       </c>
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr"/>
@@ -2792,11 +2792,11 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Tekst 139</t>
+          <t>31.05.2015</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>20661.97569919465</v>
+        <v>17294.24739957266</v>
       </c>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr"/>
@@ -2807,11 +2807,11 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Tekst 140</t>
+          <t>30.04.2015</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>19797.34928393603</v>
+        <v>16570.54781965925</v>
       </c>
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr"/>
@@ -2822,11 +2822,11 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Tekst 141</t>
+          <t>31.03.2015</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>18101.38522312723</v>
+        <v>15151.01163999205</v>
       </c>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr"/>
@@ -2837,11 +2837,11 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Tekst 142</t>
+          <t>28.02.2015</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>15301.33939520756</v>
+        <v>12807.34973741458</v>
       </c>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr"/>
@@ -2852,11 +2852,11 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Tekst 143</t>
+          <t>31.01.2015</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>20579.64808742783</v>
+        <v>17225.33849625966</v>
       </c>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr"/>
@@ -2867,11 +2867,11 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Tekst 144</t>
+          <t>31.12.2014</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>2084716.086229888</v>
+        <v>1744924.893824835</v>
       </c>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr"/>
@@ -2901,256 +2901,256 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Tekst 4</t>
+          <t>kokku_palgakulu</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>184156.9590292846</v>
+        <v>215322.9721548705</v>
       </c>
       <c r="B2" t="n">
-        <v>120861.3986010138</v>
+        <v>140630.1867999104</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>184156.0500924807</v>
+        <v>215321.9093931093</v>
       </c>
       <c r="B3" t="n">
-        <v>101432.0072201986</v>
+        <v>118022.8119811509</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>184155.1411556768</v>
+        <v>215320.8466313481</v>
       </c>
       <c r="B4" t="n">
-        <v>101002.0062432228</v>
+        <v>117522.4775615908</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>184154.2322188728</v>
+        <v>215319.7838695869</v>
       </c>
       <c r="B5" t="n">
-        <v>108376.8994430296</v>
+        <v>126103.6508751811</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>184153.3232820689</v>
+        <v>215318.7211078257</v>
       </c>
       <c r="B6" t="n">
-        <v>109298.7420832409</v>
+        <v>127176.2754202686</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>184152.414345265</v>
+        <v>215317.6583460644</v>
       </c>
       <c r="B7" t="n">
-        <v>98131.86177946825</v>
+        <v>114182.875697368</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>184151.5054084611</v>
+        <v>215316.5955843032</v>
       </c>
       <c r="B8" t="n">
-        <v>101399.8469522167</v>
+        <v>117985.3913940471</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>184070.6100329134</v>
+        <v>215222.0097875549</v>
       </c>
       <c r="B9" t="n">
-        <v>99099.52617616118</v>
+        <v>115308.8168699981</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>184069.7010961095</v>
+        <v>215220.9470257937</v>
       </c>
       <c r="B10" t="n">
-        <v>103326.68803506</v>
+        <v>120227.3977298213</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>184068.7921593055</v>
+        <v>215219.8842640325</v>
       </c>
       <c r="B11" t="n">
-        <v>111353.8453208661</v>
+        <v>129567.5232094357</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>184067.8832225016</v>
+        <v>215218.8215022713</v>
       </c>
       <c r="B12" t="n">
-        <v>99474.2167950366</v>
+        <v>115744.7940499295</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>184066.9742856977</v>
+        <v>215217.7587405101</v>
       </c>
       <c r="B13" t="n">
-        <v>100080.1939851095</v>
+        <v>116449.8883680728</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>184066.0653488938</v>
+        <v>215216.6959787488</v>
       </c>
       <c r="B14" t="n">
-        <v>105676.3493174298</v>
+        <v>122961.3831782853</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>184065.1564120899</v>
+        <v>215215.6332169876</v>
       </c>
       <c r="B15" t="n">
-        <v>98454.99008062722</v>
+        <v>114558.8567291806</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>184064.247475286</v>
+        <v>215214.5704552264</v>
       </c>
       <c r="B16" t="n">
-        <v>102093.0552107668</v>
+        <v>118791.9847978929</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>184063.3385384821</v>
+        <v>215213.5076934652</v>
       </c>
       <c r="B17" t="n">
-        <v>103925.8645591602</v>
+        <v>120924.5790257989</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>184062.4296016782</v>
+        <v>215212.444931704</v>
       </c>
       <c r="B18" t="n">
-        <v>107624.7825802152</v>
+        <v>125228.5134356243</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>184061.5206648743</v>
+        <v>215211.3821699427</v>
       </c>
       <c r="B19" t="n">
-        <v>98821.03512776921</v>
+        <v>114984.7742177469</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>184060.6117280704</v>
+        <v>215210.3194081815</v>
       </c>
       <c r="B20" t="n">
-        <v>106407.008331082</v>
+        <v>123811.5529989751</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>183979.7163525226</v>
+        <v>215115.7336114332</v>
       </c>
       <c r="B21" t="n">
-        <v>89775.84786792019</v>
+        <v>104460.1039035142</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>183978.8074157187</v>
+        <v>215114.670849672</v>
       </c>
       <c r="B22" t="n">
-        <v>106080.7504014304</v>
+        <v>123431.9304385634</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>183977.8984789148</v>
+        <v>215113.6080879108</v>
       </c>
       <c r="B23" t="n">
-        <v>103645.5557812704</v>
+        <v>120598.4213257178</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>183976.9895421109</v>
+        <v>215112.5453261496</v>
       </c>
       <c r="B24" t="n">
-        <v>98768.09601908718</v>
+        <v>114923.1760827828</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>183976.080605307</v>
+        <v>215111.4825643884</v>
       </c>
       <c r="B25" t="n">
-        <v>103234.8943088134</v>
+        <v>120120.5896917004</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>183975.1716685031</v>
+        <v>215110.4198026271</v>
       </c>
       <c r="B26" t="n">
-        <v>103492.9214217135</v>
+        <v>120420.8212090136</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>183974.2627316992</v>
+        <v>215109.3570408659</v>
       </c>
       <c r="B27" t="n">
-        <v>95892.51927810388</v>
+        <v>111577.2534067021</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>183973.3537948953</v>
+        <v>215108.2942791047</v>
       </c>
       <c r="B28" t="n">
-        <v>104200.9753791334</v>
+        <v>121244.6885599541</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>183972.4448580914</v>
+        <v>215107.2315173435</v>
       </c>
       <c r="B29" t="n">
-        <v>97857.68813197805</v>
+        <v>113863.8566250383</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>183971.5359212875</v>
+        <v>215106.1687555823</v>
       </c>
       <c r="B30" t="n">
-        <v>89323.81255718615</v>
+        <v>103934.131087342</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>183970.6269844835</v>
+        <v>215105.1059938211</v>
       </c>
       <c r="B31" t="n">
-        <v>95783.09938813794</v>
+        <v>111449.936167752</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>183969.7180476796</v>
+        <v>215104.0432320599</v>
       </c>
       <c r="B32" t="n">
-        <v>87475.31647058895</v>
+        <v>101783.2843077575</v>
       </c>
     </row>
   </sheetData>
